--- a/Application Tracker Demo.xlsx
+++ b/Application Tracker Demo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xavier Woodruff\Desktop\CAREER\EXCEL\Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:11_{126762B6-DCA8-4832-BDD9-2E1EFED8A26F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E658FCF-2B73-4858-A9B0-439E81068FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9D090ABE-52EA-4ADA-90C9-9C6A1788C0F4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="53">
   <si>
     <t>Date Applied</t>
   </si>
@@ -192,6 +192,12 @@
   </si>
   <si>
     <t>Days Pending</t>
+  </si>
+  <si>
+    <t>Accepted</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -240,7 +246,119 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="22">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -307,13 +425,13 @@
     <tableColumn id="3" xr3:uid="{26417396-0CF4-4105-A53B-92E60D1D32BC}" name="Position"/>
     <tableColumn id="4" xr3:uid="{59A45B90-A541-4D09-9E95-83F7CA64F842}" name="Code"/>
     <tableColumn id="12" xr3:uid="{17DC199A-4B87-41CA-82C1-E580612BD748}" name="Type"/>
-    <tableColumn id="14" xr3:uid="{21DAB080-4018-4BB9-8B36-1DB5B1F93640}" name="Salary" dataDxfId="5"/>
+    <tableColumn id="14" xr3:uid="{21DAB080-4018-4BB9-8B36-1DB5B1F93640}" name="Salary" dataDxfId="21"/>
     <tableColumn id="11" xr3:uid="{CC5A7DF5-BDEA-49D2-B73A-DD12C58B68AC}" name="Platform"/>
     <tableColumn id="5" xr3:uid="{DE7E47F9-7FB3-4812-BD25-3DEDE49C82FD}" name="Interview">
       <calculatedColumnFormula>IF(Table1[[#This Row],[Status]] = "Declined","No",IF(Table1[[#This Row],[Status]]= "In-Progress", "Yes", "N/A"))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{41FEBB63-52B3-47F4-B71F-8D6AD904568F}" name="Interview Date"/>
-    <tableColumn id="8" xr3:uid="{9645D385-A644-4F02-8BCB-538DCE5FE75A}" name="Days Pending" dataDxfId="4">
+    <tableColumn id="8" xr3:uid="{9645D385-A644-4F02-8BCB-538DCE5FE75A}" name="Days Pending" dataDxfId="20">
       <calculatedColumnFormula>SUM(TODAY()-Table1[[#This Row],[Date Applied]])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{931FEE81-7B64-4EF4-A467-95835F90B2AF}" name="Status"/>
@@ -726,7 +844,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="2">
         <f ca="1">SUM(TODAY()-Table1[[#This Row],[Date Applied]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L2" t="s">
         <v>7</v>
@@ -764,7 +882,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="2">
         <f ca="1">SUM(TODAY()-Table1[[#This Row],[Date Applied]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L3" t="s">
         <v>8</v>
@@ -802,7 +920,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="2">
         <f ca="1">SUM(TODAY()-Table1[[#This Row],[Date Applied]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L4" t="s">
         <v>8</v>
@@ -842,7 +960,7 @@
       </c>
       <c r="K5" s="2">
         <f ca="1">SUM(TODAY()-Table1[[#This Row],[Date Applied]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L5" t="s">
         <v>42</v>
@@ -879,7 +997,7 @@
       </c>
       <c r="K6" s="2">
         <f ca="1">SUM(TODAY()-Table1[[#This Row],[Date Applied]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L6" t="s">
         <v>7</v>
@@ -919,7 +1037,7 @@
       </c>
       <c r="K7" s="2">
         <f ca="1">SUM(TODAY()-Table1[[#This Row],[Date Applied]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L7" t="s">
         <v>42</v>
@@ -956,7 +1074,7 @@
       </c>
       <c r="K8" s="2">
         <f ca="1">SUM(TODAY()-Table1[[#This Row],[Date Applied]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L8" t="s">
         <v>7</v>
@@ -987,16 +1105,18 @@
       <c r="H9" t="s">
         <v>17</v>
       </c>
-      <c r="I9" t="str">
-        <f>IF(Table1[[#This Row],[Status]] = "Declined","No",IF(Table1[[#This Row],[Status]]= "In-Progress", "Yes", "N/A"))</f>
-        <v>N/A</v>
+      <c r="I9" t="s">
+        <v>52</v>
+      </c>
+      <c r="J9" s="1">
+        <v>46223</v>
       </c>
       <c r="K9" s="2">
         <f ca="1">SUM(TODAY()-Table1[[#This Row],[Date Applied]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L9" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1030,7 +1150,7 @@
       </c>
       <c r="K10" s="2">
         <f ca="1">SUM(TODAY()-Table1[[#This Row],[Date Applied]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L10" t="s">
         <v>7</v>
@@ -1038,7 +1158,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>46199</v>
+        <v>46138</v>
       </c>
       <c r="B11" t="s">
         <v>38</v>
@@ -1067,7 +1187,7 @@
       </c>
       <c r="K11" s="2">
         <f ca="1">SUM(TODAY()-Table1[[#This Row],[Date Applied]])</f>
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="L11" t="s">
         <v>7</v>
@@ -1104,7 +1224,7 @@
       </c>
       <c r="K12" s="2">
         <f ca="1">SUM(TODAY()-Table1[[#This Row],[Date Applied]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L12" t="s">
         <v>7</v>
@@ -1144,7 +1264,7 @@
       </c>
       <c r="K13" s="2">
         <f ca="1">SUM(TODAY()-Table1[[#This Row],[Date Applied]])</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L13" t="s">
         <v>42</v>
@@ -1170,7 +1290,7 @@
         <v>19</v>
       </c>
       <c r="G14" s="3">
-        <v>86000</v>
+        <v>75000</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
@@ -1181,7 +1301,7 @@
       </c>
       <c r="K14" s="2">
         <f ca="1">SUM(TODAY()-Table1[[#This Row],[Date Applied]])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="s">
         <v>7</v>
@@ -1189,7 +1309,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="K1:K14">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="30"/>
@@ -1201,17 +1321,29 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1:L1048576">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"In-Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
       <formula>"Declined"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"Waiting"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
       <formula>"Accepted"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:G1048576">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="formula" val="MAX($G:$G)*0.7"/>
+        <cfvo type="formula" val="MAX($G:$G)*0.85"/>
+        <cfvo type="formula" val="MAX($G:$G)"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
@@ -1229,6 +1361,9 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="I9" calculatedColumn="1"/>
+  </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
